--- a/education_surveys/045_educational_technology_access_for_rural_students_survey--education_surveys.xlsx
+++ b/education_surveys/045_educational_technology_access_for_rural_students_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1211,34 +1211,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>device_access_choices</t>
+          <t>internet_access_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>other:</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other:</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>device_access_choices</t>
+          <t>internet_access_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other:</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Other:</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1250,138 +1250,138 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other:</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other:</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>internet_access_choices</t>
+          <t>device_availability_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>internet_access_choices</t>
+          <t>device_availability_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other:</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other:</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>internet_access_choices</t>
+          <t>device_availability_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>other:</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other:</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>internet_access_choices</t>
+          <t>school_technology_availability_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>other:</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other:</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>device_availability_choices</t>
+          <t>school_technology_availability_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>device_availability_choices</t>
+          <t>teacher_technology_availability_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>device_availability_choices</t>
+          <t>teacher_technology_availability_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>school_technology_availability_choices</t>
+          <t>student_internet_access_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>school_technology_availability_choices</t>
+          <t>student_internet_access_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>teacher_technology_availability_choices</t>
+          <t>teacher_internet_access_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>teacher_technology_availability_choices</t>
+          <t>teacher_internet_access_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>student_internet_access_choices</t>
+          <t>school_wired_network_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>student_internet_access_choices</t>
+          <t>school_wired_network_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>teacher_internet_access_choices</t>
+          <t>school_wifi_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>teacher_internet_access_choices</t>
+          <t>school_wifi_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>school_wired_network_choices</t>
+          <t>school_mobile_network_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>school_wired_network_choices</t>
+          <t>school_mobile_network_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>school_wifi_choices</t>
+          <t>school_other_technology_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>school_wifi_choices</t>
+          <t>school_other_technology_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,491 +1585,423 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>school_mobile_network_choices</t>
+          <t>school_other_technology_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other:</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other:</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>school_mobile_network_choices</t>
+          <t>teacher_device_access_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>school_other_technology_choices</t>
+          <t>teacher_device_access_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>school_other_technology_choices</t>
+          <t>teacher_device_access_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other:</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other:</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>school_other_technology_choices</t>
+          <t>teacher_device_availability_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>other:</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Other:</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>teacher_device_access_choices</t>
+          <t>teacher_device_availability_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>teacher_device_access_choices</t>
+          <t>teacher_device_availability_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>teacher_device_access_choices</t>
+          <t>student_other_technology_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>other:</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Other:</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>teacher_device_availability_choices</t>
+          <t>student_other_technology_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>teacher_device_availability_choices</t>
+          <t>student_other_technology_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other:</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other:</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>teacher_device_availability_choices</t>
+          <t>student_other_device_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>student_other_technology_choices</t>
+          <t>student_other_device_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>student_other_technology_choices</t>
+          <t>student_other_device_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other:</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other:</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>student_other_technology_choices</t>
+          <t>student_device_availability_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>other:</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Other:</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>student_other_device_choices</t>
+          <t>student_device_availability_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>student_other_device_choices</t>
+          <t>student_device_availability_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>student_other_device_choices</t>
+          <t>teacher_other_device_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>other:</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Other:</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>student_device_availability_choices</t>
+          <t>teacher_other_device_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>student_device_availability_choices</t>
+          <t>teacher_other_device_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other:</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other:</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>student_device_availability_choices</t>
+          <t>teacher_other_device_availability_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>teacher_other_device_choices</t>
+          <t>teacher_other_device_availability_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>teacher_other_device_choices</t>
+          <t>teacher_other_device_availability_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>teacher_other_device_choices</t>
+          <t>student_other_device_availability_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>other:</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Other:</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>teacher_other_device_availability_choices</t>
+          <t>student_other_device_availability_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>teacher_other_device_availability_choices</t>
+          <t>student_other_device_availability_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>teacher_other_device_availability_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>student_other_device_availability_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>student_other_device_availability_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>student_other_device_availability_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
